--- a/docs/BlueFox_CUO_v2_Production_complet.xlsx
+++ b/docs/BlueFox_CUO_v2_Production_complet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Documents\Minijeu Yllias\V3_BlueFox odyssey Fondation IA\V3_EXECUTABL_fondation IA\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5ED8C3E-A524-4D20-A097-FEF84D91C74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06317E17-8973-43F7-A593-E60770DE28B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4245" yWindow="3375" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3310" uniqueCount="902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3341" uniqueCount="916">
   <si>
     <t>BlueFox Odyssey — CUO documentaire consolidé</t>
   </si>
@@ -2743,6 +2743,48 @@
   </si>
   <si>
     <t>Sans objet pour les objets persistants</t>
+  </si>
+  <si>
+    <t>Capsule</t>
+  </si>
+  <si>
+    <t>ajout</t>
+  </si>
+  <si>
+    <t>base- permanent</t>
+  </si>
+  <si>
+    <t>map Chystal</t>
+  </si>
+  <si>
+    <t>map Chystal - Zone 0</t>
+  </si>
+  <si>
+    <t>centre de la map, Zone de crash</t>
+  </si>
+  <si>
+    <t>Observer -inspect - analyse</t>
+  </si>
+  <si>
+    <t>Habitation</t>
+  </si>
+  <si>
+    <t>refuge/abri</t>
+  </si>
+  <si>
+    <t>Technology - engineering -energy</t>
+  </si>
+  <si>
+    <t>inspecter pour diagnostiquer la panne inspecter pour découvrir un plan de recherche/fabrication de composants - analyser pour découvrir une adapration possible aux réseaux d'énergie de la planète</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>à créer</t>
+  </si>
+  <si>
+    <t>forme légèrement sphérique / ovoide texture composant éléctronique et métal riveté, traces de brulure _ validation visuelle du modèle obligatoire</t>
   </si>
 </sst>
 </file>
@@ -3344,11 +3386,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CUO_Master_Table" displayName="CUO_Master_Table" ref="A1:BC56">
-  <autoFilter ref="A1:BC56" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CUO_Master_Table" displayName="CUO_Master_Table" ref="A1:BC57">
+  <autoFilter ref="A1:BC57" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="4">
       <filters>
         <filter val="constructions"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="53">
+      <filters blank="1">
+        <filter val="À discuter"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -4258,7 +4305,7 @@
         <v>66</v>
       </c>
       <c r="B7" s="7">
-        <f>COUNTA(CUO_Master!$A$2:$A$56)</f>
+        <f>COUNTA(CUO_Master!$A$2:$A$57)</f>
         <v>47</v>
       </c>
       <c r="C7" s="4"/>
@@ -4378,7 +4425,7 @@
         <v>70</v>
       </c>
       <c r="B8" s="9">
-        <f>COUNTIF(CUO_Master!$AX$2:$AX$56,"Oui")</f>
+        <f>COUNTIF(CUO_Master!$AX$2:$AX$57,"Oui")</f>
         <v>16</v>
       </c>
       <c r="C8" s="4"/>
@@ -4498,7 +4545,7 @@
         <v>73</v>
       </c>
       <c r="B9" s="9">
-        <f>COUNTIF(CUO_Master!$D$2:$D$56,"documentary")</f>
+        <f>COUNTIF(CUO_Master!$D$2:$D$57,"documentary")</f>
         <v>30</v>
       </c>
       <c r="C9" s="4"/>
@@ -4618,7 +4665,7 @@
         <v>76</v>
       </c>
       <c r="B10" s="9">
-        <f>COUNTIF(CUO_Master!$N$2:$N$56,"Oui")</f>
+        <f>COUNTIF(CUO_Master!$N$2:$N$57,"Oui")</f>
         <v>10</v>
       </c>
       <c r="C10" s="4"/>
@@ -4738,7 +4785,7 @@
         <v>79</v>
       </c>
       <c r="B11" s="10">
-        <f>COUNTIF(CUO_Master!$BB$2:$BB$56,"Validé")</f>
+        <f>COUNTIF(CUO_Master!$BB$2:$BB$57,"Validé")</f>
         <v>40</v>
       </c>
       <c r="C11" s="4"/>
@@ -5188,7 +5235,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BC56"/>
+  <dimension ref="A1:BC57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="1.125" customWidth="1"/>
@@ -12178,7 +12225,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="43" spans="1:55" ht="62.1" customHeight="1">
+    <row r="43" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A43" s="41" t="s">
         <v>714</v>
       </c>
@@ -12345,7 +12392,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="44" spans="1:55" ht="62.1" customHeight="1">
+    <row r="44" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A44" s="41" t="s">
         <v>734</v>
       </c>
@@ -12512,7 +12559,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="45" spans="1:55" ht="62.1" customHeight="1">
+    <row r="45" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A45" s="41" t="s">
         <v>752</v>
       </c>
@@ -13867,187 +13914,324 @@
         <v>811</v>
       </c>
     </row>
-    <row r="56" spans="1:55" ht="63" customHeight="1">
-      <c r="A56" s="41" t="s">
+    <row r="56" spans="1:55" ht="62.1" customHeight="1">
+      <c r="A56" s="32"/>
+      <c r="B56" s="33" t="s">
+        <v>902</v>
+      </c>
+      <c r="C56" s="33" t="s">
+        <v>902</v>
+      </c>
+      <c r="D56" s="33" t="s">
+        <v>903</v>
+      </c>
+      <c r="E56" s="33" t="s">
+        <v>432</v>
+      </c>
+      <c r="F56" s="33" t="s">
+        <v>904</v>
+      </c>
+      <c r="G56" s="33" t="s">
+        <v>434</v>
+      </c>
+      <c r="H56" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="I56" s="33" t="s">
+        <v>435</v>
+      </c>
+      <c r="J56" s="33"/>
+      <c r="K56" s="33" t="s">
+        <v>906</v>
+      </c>
+      <c r="L56" s="33"/>
+      <c r="M56" s="33" t="s">
+        <v>905</v>
+      </c>
+      <c r="N56" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O56" s="33"/>
+      <c r="P56" s="33"/>
+      <c r="Q56" s="33" t="s">
+        <v>907</v>
+      </c>
+      <c r="R56" s="33" t="s">
+        <v>705</v>
+      </c>
+      <c r="S56" s="33"/>
+      <c r="T56" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="U56" s="33" t="s">
+        <v>908</v>
+      </c>
+      <c r="V56" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="W56" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="X56" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="Y56" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z56" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="AA56" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB56" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="AC56" s="33"/>
+      <c r="AD56" s="33"/>
+      <c r="AE56" s="33"/>
+      <c r="AF56" s="33" t="s">
+        <v>910</v>
+      </c>
+      <c r="AG56" s="33" t="s">
+        <v>909</v>
+      </c>
+      <c r="AH56" s="33" t="s">
+        <v>911</v>
+      </c>
+      <c r="AI56" s="33"/>
+      <c r="AJ56" s="33" t="s">
+        <v>912</v>
+      </c>
+      <c r="AK56" s="33"/>
+      <c r="AL56" s="33"/>
+      <c r="AM56" s="39">
+        <v>4</v>
+      </c>
+      <c r="AN56" s="39">
+        <v>3</v>
+      </c>
+      <c r="AO56" s="39">
+        <v>4</v>
+      </c>
+      <c r="AP56" s="39">
+        <v>0</v>
+      </c>
+      <c r="AQ56" s="39">
+        <v>12</v>
+      </c>
+      <c r="AR56" s="39">
+        <v>0.8</v>
+      </c>
+      <c r="AS56" s="33" t="s">
+        <v>913</v>
+      </c>
+      <c r="AT56" s="39">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AU56" s="39">
+        <v>0.25</v>
+      </c>
+      <c r="AV56" s="39">
+        <v>0.08</v>
+      </c>
+      <c r="AW56" s="33" t="s">
+        <v>903</v>
+      </c>
+      <c r="AX56" s="33" t="s">
+        <v>914</v>
+      </c>
+      <c r="AY56" s="33"/>
+      <c r="AZ56" s="33"/>
+      <c r="BA56" s="33"/>
+      <c r="BB56" s="33" t="s">
+        <v>385</v>
+      </c>
+      <c r="BC56" s="34" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="57" spans="1:55" ht="63" hidden="1" customHeight="1">
+      <c r="A57" s="41" t="s">
         <v>812</v>
       </c>
-      <c r="B56" s="42" t="s">
+      <c r="B57" s="42" t="s">
         <v>813</v>
       </c>
-      <c r="C56" s="42" t="s">
+      <c r="C57" s="42" t="s">
         <v>814</v>
       </c>
-      <c r="D56" s="42" t="s">
+      <c r="D57" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="E56" s="42" t="s">
+      <c r="E57" s="42" t="s">
         <v>432</v>
       </c>
-      <c r="F56" s="42" t="s">
+      <c r="F57" s="42" t="s">
         <v>815</v>
       </c>
-      <c r="G56" s="42" t="s">
+      <c r="G57" s="42" t="s">
         <v>434</v>
       </c>
-      <c r="H56" s="42" t="s">
+      <c r="H57" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="I56" s="42" t="s">
+      <c r="I57" s="42" t="s">
         <v>143</v>
       </c>
-      <c r="J56" s="42" t="s">
+      <c r="J57" s="42" t="s">
         <v>816</v>
       </c>
-      <c r="K56" s="42" t="s">
+      <c r="K57" s="42" t="s">
         <v>817</v>
       </c>
-      <c r="L56" s="42" t="s">
+      <c r="L57" s="42" t="s">
         <v>817</v>
       </c>
-      <c r="M56" s="42" t="s">
+      <c r="M57" s="42" t="s">
         <v>818</v>
       </c>
-      <c r="N56" s="42" t="s">
+      <c r="N57" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="O56" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="P56" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q56" s="42" t="s">
+      <c r="O57" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="P57" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q57" s="42" t="s">
         <v>819</v>
       </c>
-      <c r="R56" s="42" t="s">
+      <c r="R57" s="42" t="s">
         <v>820</v>
       </c>
-      <c r="S56" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="T56" s="42" t="s">
+      <c r="S57" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="T57" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="U56" s="42" t="s">
+      <c r="U57" s="42" t="s">
         <v>821</v>
       </c>
-      <c r="V56" s="42" t="s">
+      <c r="V57" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="W56" s="42" t="s">
+      <c r="W57" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="X56" s="42" t="s">
+      <c r="X57" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="Y56" s="42" t="s">
+      <c r="Y57" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="Z56" s="42" t="s">
+      <c r="Z57" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="AA56" s="42" t="s">
+      <c r="AA57" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="AB56" s="42" t="s">
+      <c r="AB57" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="AC56" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="AD56" s="42" t="s">
+      <c r="AC57" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD57" s="42" t="s">
         <v>822</v>
       </c>
-      <c r="AE56" s="42" t="s">
+      <c r="AE57" s="42" t="s">
         <v>815</v>
       </c>
-      <c r="AF56" s="42" t="s">
+      <c r="AF57" s="42" t="s">
         <v>823</v>
       </c>
-      <c r="AG56" s="42" t="s">
+      <c r="AG57" s="42" t="s">
         <v>824</v>
       </c>
-      <c r="AH56" s="42" t="s">
+      <c r="AH57" s="42" t="s">
         <v>825</v>
       </c>
-      <c r="AI56" s="42" t="s">
+      <c r="AI57" s="42" t="s">
         <v>329</v>
       </c>
-      <c r="AJ56" s="42" t="s">
+      <c r="AJ57" s="42" t="s">
         <v>826</v>
       </c>
-      <c r="AK56" s="42" t="s">
+      <c r="AK57" s="42" t="s">
         <v>827</v>
       </c>
-      <c r="AL56" s="42" t="s">
+      <c r="AL57" s="42" t="s">
         <v>828</v>
       </c>
-      <c r="AM56" s="42">
+      <c r="AM57" s="42">
         <v>2</v>
       </c>
-      <c r="AN56" s="42">
+      <c r="AN57" s="42">
         <v>20</v>
       </c>
-      <c r="AO56" s="42">
+      <c r="AO57" s="42">
         <v>0.4</v>
       </c>
-      <c r="AP56" s="42">
+      <c r="AP57" s="42">
         <v>0</v>
       </c>
-      <c r="AQ56" s="42">
+      <c r="AQ57" s="42">
         <v>35</v>
       </c>
-      <c r="AR56" s="42">
+      <c r="AR57" s="42">
         <v>0.65</v>
       </c>
-      <c r="AS56" s="42" t="s">
+      <c r="AS57" s="42" t="s">
         <v>184</v>
       </c>
-      <c r="AT56" s="42">
+      <c r="AT57" s="42">
         <v>0.25</v>
       </c>
-      <c r="AU56" s="42">
+      <c r="AU57" s="42">
         <v>0.85</v>
       </c>
-      <c r="AV56" s="42">
+      <c r="AV57" s="42">
         <v>0</v>
       </c>
-      <c r="AW56" s="42" t="s">
+      <c r="AW57" s="42" t="s">
         <v>329</v>
       </c>
-      <c r="AX56" s="42" t="s">
+      <c r="AX57" s="42" t="s">
         <v>731</v>
       </c>
-      <c r="AY56" s="42" t="s">
+      <c r="AY57" s="42" t="s">
         <v>732</v>
       </c>
-      <c r="AZ56" s="42" t="s">
+      <c r="AZ57" s="42" t="s">
         <v>165</v>
       </c>
-      <c r="BA56" s="42" t="s">
+      <c r="BA57" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="BB56" s="42" t="s">
+      <c r="BB57" s="42" t="s">
         <v>166</v>
       </c>
-      <c r="BC56" s="43" t="s">
+      <c r="BC57" s="43" t="s">
         <v>829</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AY2:AY56">
+  <conditionalFormatting sqref="AY2:AY57">
     <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Mixte"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB2:BB56">
+  <conditionalFormatting sqref="BB2:BB57">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Validé"/>
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="À corriger"/>
     <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="À valider"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="BB2:BB56" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="BB2:BB57" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"À valider,Validé,À corriger,Refusé,À discuter"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="BA2:BA56" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" sqref="BA2:BA57" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/BlueFox_CUO_v2_Production_complet.xlsx
+++ b/docs/BlueFox_CUO_v2_Production_complet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Documents\Minijeu Yllias\V3_BlueFox odyssey Fondation IA\V3_EXECUTABL_fondation IA\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06317E17-8973-43F7-A593-E60770DE28B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADD4399-372D-49CB-979F-A6B09D32F973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4245" yWindow="3375" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="1" r:id="rId1"/>
@@ -1374,9 +1374,6 @@
     <t>CUO V1 — objet exemple; spécification du refuge principal</t>
   </si>
   <si>
-    <t>Habitation spéciale — validation visuelle du modèle obligatoire - faire propositions à valider</t>
-  </si>
-  <si>
     <t>DOC-NAT-CTRE-L-001</t>
   </si>
   <si>
@@ -2076,9 +2073,6 @@
     <t>Cahier des charges §19.1; missions historiques</t>
   </si>
   <si>
-    <t>Structure spéciale — validation visuelle du modèle obligatoire</t>
-  </si>
-  <si>
     <t>DOC-CON-SECB-L-001</t>
   </si>
   <si>
@@ -2115,9 +2109,6 @@
     <t>Spécification documentaire — bases secondaires</t>
   </si>
   <si>
-    <t>Habitation spéciale — validation visuelle du modèle obligatoire</t>
-  </si>
-  <si>
     <t>Bush</t>
   </si>
   <si>
@@ -2784,7 +2775,16 @@
     <t>à créer</t>
   </si>
   <si>
-    <t>forme légèrement sphérique / ovoide texture composant éléctronique et métal riveté, traces de brulure _ validation visuelle du modèle obligatoire</t>
+    <t>Habitation spéciale ——  déjà intégré : micro scène custom</t>
+  </si>
+  <si>
+    <t>forme légèrement sphérique / ovoide texture composant éléctronique et métal riveté, traces de brulure _—  déjà intégré</t>
+  </si>
+  <si>
+    <t>Structure spéciale —  déjà intégré : micro-scène custom camp de base renforcé étape 3</t>
+  </si>
+  <si>
+    <t>Habitation spéciale —  déjà intégré : micro scène custom camp de basse renforcé étape 2  dupliquable sur les autres maps selon la progression camp puis camp de base.  + prérequis de distance avec le site du crash et autres prérequis fixés explicitement.</t>
   </si>
 </sst>
 </file>
@@ -3388,13 +3388,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CUO_Master_Table" displayName="CUO_Master_Table" ref="A1:BC57">
   <autoFilter ref="A1:BC57" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="4">
+    <filterColumn colId="53">
       <filters>
-        <filter val="constructions"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="53">
-      <filters blank="1">
         <filter val="À discuter"/>
       </filters>
     </filterColumn>
@@ -4786,7 +4781,7 @@
       </c>
       <c r="B11" s="10">
         <f>COUNTIF(CUO_Master!$BB$2:$BB$57,"Validé")</f>
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -7933,7 +7928,7 @@
       </c>
       <c r="BC16" s="34"/>
     </row>
-    <row r="17" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    <row r="17" spans="1:55" ht="62.1" customHeight="1">
       <c r="A17" s="32" t="s">
         <v>368</v>
       </c>
@@ -8434,7 +8429,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="20" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    <row r="20" spans="1:55" ht="62.1" customHeight="1">
       <c r="A20" s="32" t="s">
         <v>414</v>
       </c>
@@ -8764,19 +8759,19 @@
       <c r="BB21" s="33" t="s">
         <v>385</v>
       </c>
-      <c r="BC21" s="36" t="s">
-        <v>445</v>
+      <c r="BC21" s="34" t="s">
+        <v>912</v>
       </c>
     </row>
     <row r="22" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A22" s="32" t="s">
+        <v>445</v>
+      </c>
+      <c r="B22" s="33" t="s">
         <v>446</v>
       </c>
-      <c r="B22" s="33" t="s">
+      <c r="C22" s="33" t="s">
         <v>447</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>448</v>
       </c>
       <c r="D22" s="33" t="s">
         <v>326</v>
@@ -8785,10 +8780,10 @@
         <v>239</v>
       </c>
       <c r="F22" s="33" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G22" s="33" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H22" s="33" t="s">
         <v>257</v>
@@ -8806,22 +8801,22 @@
         <v>149</v>
       </c>
       <c r="M22" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="N22" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O22" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P22" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q22" s="33" t="s">
         <v>450</v>
       </c>
-      <c r="N22" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O22" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P22" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q22" s="33" t="s">
+      <c r="R22" s="33" t="s">
         <v>451</v>
-      </c>
-      <c r="R22" s="33" t="s">
-        <v>452</v>
       </c>
       <c r="S22" s="33" t="s">
         <v>149</v>
@@ -8869,19 +8864,19 @@
         <v>179</v>
       </c>
       <c r="AH22" s="33" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AI22" s="33" t="s">
         <v>380</v>
       </c>
       <c r="AJ22" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AK22" s="33" t="s">
         <v>382</v>
       </c>
       <c r="AL22" s="33" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AM22" s="33">
         <v>4</v>
@@ -8920,7 +8915,7 @@
         <v>43</v>
       </c>
       <c r="AY22" s="33" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AZ22" s="33" t="s">
         <v>165</v>
@@ -8937,13 +8932,13 @@
     </row>
     <row r="23" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A23" s="32" t="s">
+        <v>456</v>
+      </c>
+      <c r="B23" s="33" t="s">
         <v>457</v>
       </c>
-      <c r="B23" s="33" t="s">
+      <c r="C23" s="33" t="s">
         <v>458</v>
-      </c>
-      <c r="C23" s="33" t="s">
-        <v>459</v>
       </c>
       <c r="D23" s="33" t="s">
         <v>326</v>
@@ -8952,7 +8947,7 @@
         <v>239</v>
       </c>
       <c r="F23" s="33" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G23" s="33" t="s">
         <v>179</v>
@@ -8973,31 +8968,31 @@
         <v>149</v>
       </c>
       <c r="M23" s="33" t="s">
+        <v>460</v>
+      </c>
+      <c r="N23" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O23" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P23" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q23" s="33" t="s">
         <v>461</v>
       </c>
-      <c r="N23" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O23" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P23" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q23" s="33" t="s">
+      <c r="R23" s="33" t="s">
         <v>462</v>
       </c>
-      <c r="R23" s="33" t="s">
+      <c r="S23" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="T23" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="U23" s="33" t="s">
         <v>463</v>
-      </c>
-      <c r="S23" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="T23" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="U23" s="33" t="s">
-        <v>464</v>
       </c>
       <c r="V23" s="33" t="s">
         <v>375</v>
@@ -9027,7 +9022,7 @@
         <v>60</v>
       </c>
       <c r="AE23" s="33" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AF23" s="33" t="s">
         <v>178</v>
@@ -9036,19 +9031,19 @@
         <v>179</v>
       </c>
       <c r="AH23" s="33" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AI23" s="33" t="s">
         <v>380</v>
       </c>
       <c r="AJ23" s="33" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AK23" s="33" t="s">
         <v>382</v>
       </c>
       <c r="AL23" s="33" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AM23" s="39">
         <v>10</v>
@@ -9087,7 +9082,7 @@
         <v>43</v>
       </c>
       <c r="AY23" s="33" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AZ23" s="33" t="s">
         <v>165</v>
@@ -9107,22 +9102,22 @@
         <v>253</v>
       </c>
       <c r="B24" s="33" t="s">
+        <v>468</v>
+      </c>
+      <c r="C24" s="33" t="s">
         <v>469</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>470</v>
       </c>
       <c r="D24" s="33" t="s">
         <v>326</v>
       </c>
       <c r="E24" s="33" t="s">
+        <v>470</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>468</v>
+      </c>
+      <c r="G24" s="33" t="s">
         <v>471</v>
-      </c>
-      <c r="F24" s="33" t="s">
-        <v>469</v>
-      </c>
-      <c r="G24" s="33" t="s">
-        <v>472</v>
       </c>
       <c r="H24" s="33" t="s">
         <v>142</v>
@@ -9136,7 +9131,7 @@
         <v>149</v>
       </c>
       <c r="M24" s="33" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="N24" s="33" t="s">
         <v>43</v>
@@ -9146,17 +9141,17 @@
       </c>
       <c r="P24" s="33"/>
       <c r="Q24" s="33" t="s">
+        <v>473</v>
+      </c>
+      <c r="R24" s="33" t="s">
         <v>474</v>
-      </c>
-      <c r="R24" s="33" t="s">
-        <v>475</v>
       </c>
       <c r="S24" s="33"/>
       <c r="T24" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="U24" s="33" t="s">
         <v>476</v>
-      </c>
-      <c r="U24" s="33" t="s">
-        <v>477</v>
       </c>
       <c r="V24" s="33" t="s">
         <v>40</v>
@@ -9189,7 +9184,7 @@
         <v>149</v>
       </c>
       <c r="AF24" s="33" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AG24" s="33" t="s">
         <v>179</v>
@@ -9198,16 +9193,16 @@
         <v>262</v>
       </c>
       <c r="AI24" s="33" t="s">
+        <v>478</v>
+      </c>
+      <c r="AJ24" s="33" t="s">
         <v>479</v>
       </c>
-      <c r="AJ24" s="33" t="s">
+      <c r="AK24" s="33" t="s">
+        <v>478</v>
+      </c>
+      <c r="AL24" s="33" t="s">
         <v>480</v>
-      </c>
-      <c r="AK24" s="33" t="s">
-        <v>479</v>
-      </c>
-      <c r="AL24" s="33" t="s">
-        <v>481</v>
       </c>
       <c r="AM24" s="33">
         <v>4</v>
@@ -9228,7 +9223,7 @@
         <v>1.25</v>
       </c>
       <c r="AS24" s="33" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AT24" s="33">
         <v>1</v>
@@ -9258,18 +9253,18 @@
         <v>166</v>
       </c>
       <c r="BC24" s="34" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="25" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A25" s="32" t="s">
+        <v>483</v>
+      </c>
+      <c r="B25" s="33" t="s">
         <v>484</v>
       </c>
-      <c r="B25" s="33" t="s">
+      <c r="C25" s="33" t="s">
         <v>485</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>486</v>
       </c>
       <c r="D25" s="33" t="s">
         <v>326</v>
@@ -9278,7 +9273,7 @@
         <v>239</v>
       </c>
       <c r="F25" s="33" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G25" s="33" t="s">
         <v>179</v>
@@ -9299,31 +9294,31 @@
         <v>149</v>
       </c>
       <c r="M25" s="33" t="s">
+        <v>487</v>
+      </c>
+      <c r="N25" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O25" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P25" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q25" s="33" t="s">
         <v>488</v>
       </c>
-      <c r="N25" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O25" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P25" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q25" s="33" t="s">
+      <c r="R25" s="33" t="s">
         <v>489</v>
       </c>
-      <c r="R25" s="33" t="s">
+      <c r="S25" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="T25" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="U25" s="33" t="s">
         <v>490</v>
-      </c>
-      <c r="S25" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="T25" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="U25" s="33" t="s">
-        <v>491</v>
       </c>
       <c r="V25" s="33" t="s">
         <v>375</v>
@@ -9353,7 +9348,7 @@
         <v>210</v>
       </c>
       <c r="AE25" s="33" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AF25" s="33" t="s">
         <v>178</v>
@@ -9362,19 +9357,19 @@
         <v>179</v>
       </c>
       <c r="AH25" s="33" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AI25" s="33" t="s">
         <v>380</v>
       </c>
       <c r="AJ25" s="33" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AK25" s="33" t="s">
         <v>382</v>
       </c>
       <c r="AL25" s="33" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AM25" s="33">
         <v>6</v>
@@ -9413,7 +9408,7 @@
         <v>43</v>
       </c>
       <c r="AY25" s="33" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AZ25" s="33" t="s">
         <v>165</v>
@@ -9425,30 +9420,30 @@
         <v>166</v>
       </c>
       <c r="BC25" s="34" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="26" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A26" s="32" t="s">
+        <v>496</v>
+      </c>
+      <c r="B26" s="33" t="s">
         <v>497</v>
       </c>
-      <c r="B26" s="33" t="s">
+      <c r="C26" s="33" t="s">
         <v>498</v>
-      </c>
-      <c r="C26" s="33" t="s">
-        <v>499</v>
       </c>
       <c r="D26" s="33" t="s">
         <v>326</v>
       </c>
       <c r="E26" s="33" t="s">
+        <v>499</v>
+      </c>
+      <c r="F26" s="33" t="s">
         <v>500</v>
       </c>
-      <c r="F26" s="33" t="s">
+      <c r="G26" s="33" t="s">
         <v>501</v>
-      </c>
-      <c r="G26" s="33" t="s">
-        <v>502</v>
       </c>
       <c r="H26" s="33" t="s">
         <v>285</v>
@@ -9466,31 +9461,31 @@
         <v>149</v>
       </c>
       <c r="M26" s="33" t="s">
+        <v>502</v>
+      </c>
+      <c r="N26" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O26" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P26" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q26" s="33" t="s">
         <v>503</v>
       </c>
-      <c r="N26" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O26" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P26" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q26" s="33" t="s">
+      <c r="R26" s="33" t="s">
         <v>504</v>
       </c>
-      <c r="R26" s="33" t="s">
+      <c r="S26" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="T26" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="U26" s="33" t="s">
         <v>505</v>
-      </c>
-      <c r="S26" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="T26" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="U26" s="33" t="s">
-        <v>506</v>
       </c>
       <c r="V26" s="33" t="s">
         <v>375</v>
@@ -9523,25 +9518,25 @@
         <v>149</v>
       </c>
       <c r="AF26" s="33" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG26" s="33" t="s">
         <v>299</v>
       </c>
       <c r="AH26" s="33" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AI26" s="33" t="s">
         <v>380</v>
       </c>
       <c r="AJ26" s="33" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AK26" s="33" t="s">
         <v>382</v>
       </c>
       <c r="AL26" s="33" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AM26" s="39">
         <v>10</v>
@@ -9580,7 +9575,7 @@
         <v>43</v>
       </c>
       <c r="AY26" s="33" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AZ26" s="33" t="s">
         <v>165</v>
@@ -9592,30 +9587,30 @@
         <v>166</v>
       </c>
       <c r="BC26" s="34" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="27" spans="1:55" ht="62.1" customHeight="1">
+      <c r="A27" s="32" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="27" spans="1:55" ht="62.1" hidden="1" customHeight="1">
-      <c r="A27" s="32" t="s">
+      <c r="B27" s="33" t="s">
         <v>512</v>
       </c>
-      <c r="B27" s="33" t="s">
+      <c r="C27" s="33" t="s">
         <v>513</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>514</v>
       </c>
       <c r="D27" s="33" t="s">
         <v>326</v>
       </c>
       <c r="E27" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="F27" s="33" t="s">
         <v>515</v>
       </c>
-      <c r="F27" s="33" t="s">
-        <v>516</v>
-      </c>
       <c r="G27" s="33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H27" s="33" t="s">
         <v>142</v>
@@ -9633,31 +9628,31 @@
         <v>149</v>
       </c>
       <c r="M27" s="33" t="s">
+        <v>516</v>
+      </c>
+      <c r="N27" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O27" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P27" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q27" s="33" t="s">
         <v>517</v>
       </c>
-      <c r="N27" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O27" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P27" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q27" s="33" t="s">
+      <c r="R27" s="33" t="s">
         <v>518</v>
       </c>
-      <c r="R27" s="33" t="s">
+      <c r="S27" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="T27" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="U27" s="33" t="s">
         <v>519</v>
-      </c>
-      <c r="S27" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="T27" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="U27" s="33" t="s">
-        <v>520</v>
       </c>
       <c r="V27" s="33" t="s">
         <v>375</v>
@@ -9690,25 +9685,25 @@
         <v>149</v>
       </c>
       <c r="AF27" s="33" t="s">
+        <v>520</v>
+      </c>
+      <c r="AG27" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="AH27" s="33" t="s">
         <v>521</v>
-      </c>
-      <c r="AG27" s="33" t="s">
-        <v>515</v>
-      </c>
-      <c r="AH27" s="33" t="s">
-        <v>522</v>
       </c>
       <c r="AI27" s="33" t="s">
         <v>380</v>
       </c>
       <c r="AJ27" s="33" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AK27" s="33" t="s">
         <v>382</v>
       </c>
       <c r="AL27" s="33" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AM27" s="39">
         <v>10</v>
@@ -9747,7 +9742,7 @@
         <v>43</v>
       </c>
       <c r="AY27" s="33" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AZ27" s="33" t="s">
         <v>165</v>
@@ -9759,18 +9754,18 @@
         <v>385</v>
       </c>
       <c r="BC27" s="34" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="28" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A28" s="32" t="s">
+        <v>525</v>
+      </c>
+      <c r="B28" s="33" t="s">
         <v>526</v>
       </c>
-      <c r="B28" s="33" t="s">
+      <c r="C28" s="33" t="s">
         <v>527</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>528</v>
       </c>
       <c r="D28" s="33" t="s">
         <v>326</v>
@@ -9779,7 +9774,7 @@
         <v>140</v>
       </c>
       <c r="F28" s="33" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G28" s="33" t="s">
         <v>205</v>
@@ -9800,23 +9795,23 @@
         <v>149</v>
       </c>
       <c r="M28" s="33" t="s">
+        <v>529</v>
+      </c>
+      <c r="N28" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O28" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P28" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q28" s="33" t="s">
         <v>530</v>
       </c>
-      <c r="N28" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O28" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P28" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q28" s="33" t="s">
+      <c r="R28" s="33" t="s">
         <v>531</v>
       </c>
-      <c r="R28" s="33" t="s">
-        <v>532</v>
-      </c>
       <c r="S28" s="33" t="s">
         <v>149</v>
       </c>
@@ -9824,7 +9819,7 @@
         <v>149</v>
       </c>
       <c r="U28" s="33" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="V28" s="33" t="s">
         <v>375</v>
@@ -9854,28 +9849,28 @@
         <v>180</v>
       </c>
       <c r="AE28" s="33" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AF28" s="33" t="s">
         <v>178</v>
       </c>
       <c r="AG28" s="33" t="s">
+        <v>533</v>
+      </c>
+      <c r="AH28" s="35" t="s">
         <v>534</v>
-      </c>
-      <c r="AH28" s="35" t="s">
-        <v>535</v>
       </c>
       <c r="AI28" s="33" t="s">
         <v>380</v>
       </c>
       <c r="AJ28" s="33" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AK28" s="33" t="s">
         <v>382</v>
       </c>
       <c r="AL28" s="33" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AM28" s="33">
         <v>1</v>
@@ -9914,7 +9909,7 @@
         <v>43</v>
       </c>
       <c r="AY28" s="33" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AZ28" s="33" t="s">
         <v>165</v>
@@ -9926,27 +9921,27 @@
         <v>166</v>
       </c>
       <c r="BC28" s="36" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="29" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A29" s="32" t="s">
+        <v>538</v>
+      </c>
+      <c r="B29" s="33" t="s">
         <v>539</v>
       </c>
-      <c r="B29" s="33" t="s">
+      <c r="C29" s="33" t="s">
         <v>540</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>541</v>
       </c>
       <c r="D29" s="33" t="s">
         <v>326</v>
       </c>
       <c r="E29" s="33" t="s">
+        <v>541</v>
+      </c>
+      <c r="F29" s="33" t="s">
         <v>542</v>
-      </c>
-      <c r="F29" s="33" t="s">
-        <v>543</v>
       </c>
       <c r="G29" s="33" t="s">
         <v>241</v>
@@ -9967,31 +9962,31 @@
         <v>149</v>
       </c>
       <c r="M29" s="33" t="s">
+        <v>543</v>
+      </c>
+      <c r="N29" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O29" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P29" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q29" s="33" t="s">
         <v>544</v>
       </c>
-      <c r="N29" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O29" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P29" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q29" s="33" t="s">
+      <c r="R29" s="33" t="s">
         <v>545</v>
       </c>
-      <c r="R29" s="33" t="s">
+      <c r="S29" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="T29" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="U29" s="33" t="s">
         <v>546</v>
-      </c>
-      <c r="S29" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="T29" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="U29" s="33" t="s">
-        <v>547</v>
       </c>
       <c r="V29" s="33" t="s">
         <v>375</v>
@@ -10024,7 +10019,7 @@
         <v>149</v>
       </c>
       <c r="AF29" s="33" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG29" s="33" t="s">
         <v>241</v>
@@ -10036,13 +10031,13 @@
         <v>380</v>
       </c>
       <c r="AJ29" s="33" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AK29" s="33" t="s">
         <v>382</v>
       </c>
       <c r="AL29" s="33" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AM29" s="39">
         <v>10</v>
@@ -10081,7 +10076,7 @@
         <v>43</v>
       </c>
       <c r="AY29" s="33" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AZ29" s="33" t="s">
         <v>165</v>
@@ -10093,30 +10088,30 @@
         <v>166</v>
       </c>
       <c r="BC29" s="34" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="30" spans="1:55" ht="62.1" customHeight="1">
+      <c r="A30" s="32" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="30" spans="1:55" ht="62.1" hidden="1" customHeight="1">
-      <c r="A30" s="32" t="s">
+      <c r="B30" s="33" t="s">
         <v>553</v>
       </c>
-      <c r="B30" s="33" t="s">
+      <c r="C30" s="33" t="s">
         <v>554</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>555</v>
       </c>
       <c r="D30" s="33" t="s">
         <v>326</v>
       </c>
       <c r="E30" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="F30" s="33" t="s">
+        <v>553</v>
+      </c>
+      <c r="G30" s="33" t="s">
         <v>556</v>
-      </c>
-      <c r="F30" s="33" t="s">
-        <v>554</v>
-      </c>
-      <c r="G30" s="33" t="s">
-        <v>557</v>
       </c>
       <c r="H30" s="33" t="s">
         <v>285</v>
@@ -10134,31 +10129,31 @@
         <v>149</v>
       </c>
       <c r="M30" s="35" t="s">
+        <v>557</v>
+      </c>
+      <c r="N30" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O30" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P30" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q30" s="33" t="s">
         <v>558</v>
       </c>
-      <c r="N30" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O30" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P30" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q30" s="33" t="s">
+      <c r="R30" s="33" t="s">
         <v>559</v>
       </c>
-      <c r="R30" s="33" t="s">
+      <c r="S30" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="T30" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="U30" s="33" t="s">
         <v>560</v>
-      </c>
-      <c r="S30" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="T30" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="U30" s="33" t="s">
-        <v>561</v>
       </c>
       <c r="V30" s="33" t="s">
         <v>375</v>
@@ -10197,19 +10192,19 @@
         <v>299</v>
       </c>
       <c r="AH30" s="33" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AI30" s="33" t="s">
         <v>380</v>
       </c>
       <c r="AJ30" s="33" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AK30" s="33" t="s">
         <v>382</v>
       </c>
       <c r="AL30" s="33" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AM30" s="33">
         <v>6</v>
@@ -10239,7 +10234,7 @@
         <v>0</v>
       </c>
       <c r="AV30" s="33" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AW30" s="33" t="s">
         <v>329</v>
@@ -10248,7 +10243,7 @@
         <v>43</v>
       </c>
       <c r="AY30" s="33" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AZ30" s="33" t="s">
         <v>165</v>
@@ -10260,18 +10255,18 @@
         <v>385</v>
       </c>
       <c r="BC30" s="34" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="31" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A31" s="32" t="s">
+        <v>566</v>
+      </c>
+      <c r="B31" s="33" t="s">
         <v>567</v>
       </c>
-      <c r="B31" s="33" t="s">
+      <c r="C31" s="33" t="s">
         <v>568</v>
-      </c>
-      <c r="C31" s="33" t="s">
-        <v>569</v>
       </c>
       <c r="D31" s="33" t="s">
         <v>326</v>
@@ -10280,7 +10275,7 @@
         <v>270</v>
       </c>
       <c r="F31" s="33" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G31" s="33" t="s">
         <v>222</v>
@@ -10301,31 +10296,31 @@
         <v>149</v>
       </c>
       <c r="M31" s="35" t="s">
+        <v>569</v>
+      </c>
+      <c r="N31" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O31" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P31" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q31" s="33" t="s">
         <v>570</v>
       </c>
-      <c r="N31" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O31" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P31" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q31" s="33" t="s">
+      <c r="R31" s="33" t="s">
         <v>571</v>
       </c>
-      <c r="R31" s="33" t="s">
+      <c r="S31" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="T31" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="U31" s="33" t="s">
         <v>572</v>
-      </c>
-      <c r="S31" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="T31" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="U31" s="33" t="s">
-        <v>573</v>
       </c>
       <c r="V31" s="33" t="s">
         <v>375</v>
@@ -10352,31 +10347,31 @@
         <v>149</v>
       </c>
       <c r="AD31" s="35" t="s">
+        <v>573</v>
+      </c>
+      <c r="AE31" s="33" t="s">
         <v>574</v>
       </c>
-      <c r="AE31" s="33" t="s">
+      <c r="AF31" s="33" t="s">
         <v>575</v>
-      </c>
-      <c r="AF31" s="33" t="s">
-        <v>576</v>
       </c>
       <c r="AG31" s="33" t="s">
         <v>222</v>
       </c>
       <c r="AH31" s="33" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AI31" s="33" t="s">
         <v>380</v>
       </c>
       <c r="AJ31" s="35" t="s">
+        <v>577</v>
+      </c>
+      <c r="AK31" s="35" t="s">
         <v>578</v>
       </c>
-      <c r="AK31" s="35" t="s">
+      <c r="AL31" s="33" t="s">
         <v>579</v>
-      </c>
-      <c r="AL31" s="33" t="s">
-        <v>580</v>
       </c>
       <c r="AM31" s="33">
         <v>6</v>
@@ -10415,7 +10410,7 @@
         <v>43</v>
       </c>
       <c r="AY31" s="33" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AZ31" s="33" t="s">
         <v>165</v>
@@ -10427,72 +10422,72 @@
         <v>166</v>
       </c>
       <c r="BC31" s="36" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="32" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A32" s="32" t="s">
+        <v>581</v>
+      </c>
+      <c r="B32" s="33" t="s">
         <v>582</v>
       </c>
-      <c r="B32" s="33" t="s">
+      <c r="C32" s="33" t="s">
         <v>583</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>584</v>
       </c>
       <c r="D32" s="33" t="s">
         <v>326</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F32" s="33" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G32" s="33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H32" s="33" t="s">
         <v>171</v>
       </c>
       <c r="I32" s="33" t="s">
+        <v>585</v>
+      </c>
+      <c r="J32" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="K32" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="L32" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="M32" s="33" t="s">
         <v>586</v>
       </c>
-      <c r="J32" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="K32" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="L32" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="M32" s="33" t="s">
+      <c r="N32" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O32" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P32" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q32" s="33" t="s">
         <v>587</v>
       </c>
-      <c r="N32" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O32" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P32" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q32" s="33" t="s">
+      <c r="R32" s="33" t="s">
         <v>588</v>
       </c>
-      <c r="R32" s="33" t="s">
+      <c r="S32" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="T32" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="U32" s="33" t="s">
         <v>589</v>
-      </c>
-      <c r="S32" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="T32" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="U32" s="33" t="s">
-        <v>590</v>
       </c>
       <c r="V32" s="33" t="s">
         <v>375</v>
@@ -10525,23 +10520,23 @@
         <v>149</v>
       </c>
       <c r="AF32" s="33" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG32" s="33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AH32" s="33" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AI32" s="33"/>
       <c r="AJ32" s="33" t="s">
+        <v>591</v>
+      </c>
+      <c r="AK32" s="33" t="s">
         <v>592</v>
       </c>
-      <c r="AK32" s="33" t="s">
+      <c r="AL32" s="33" t="s">
         <v>593</v>
-      </c>
-      <c r="AL32" s="33" t="s">
-        <v>594</v>
       </c>
       <c r="AM32" s="39">
         <v>10</v>
@@ -10580,7 +10575,7 @@
         <v>43</v>
       </c>
       <c r="AY32" s="33" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AZ32" s="33" t="s">
         <v>165</v>
@@ -10592,72 +10587,72 @@
         <v>166</v>
       </c>
       <c r="BC32" s="34" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="33" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A33" s="32" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B33" s="33" t="s">
+        <v>596</v>
+      </c>
+      <c r="C33" s="33" t="s">
         <v>597</v>
-      </c>
-      <c r="C33" s="33" t="s">
-        <v>598</v>
       </c>
       <c r="D33" s="33" t="s">
         <v>326</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F33" s="33" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G33" s="33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H33" s="33" t="s">
         <v>171</v>
       </c>
       <c r="I33" s="33" t="s">
+        <v>585</v>
+      </c>
+      <c r="J33" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="K33" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="L33" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="M33" s="33" t="s">
         <v>586</v>
       </c>
-      <c r="J33" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="K33" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="L33" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="M33" s="33" t="s">
+      <c r="N33" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O33" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P33" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q33" s="33" t="s">
         <v>587</v>
       </c>
-      <c r="N33" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O33" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P33" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q33" s="33" t="s">
+      <c r="R33" s="33" t="s">
         <v>588</v>
       </c>
-      <c r="R33" s="33" t="s">
+      <c r="S33" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="T33" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="U33" s="33" t="s">
         <v>589</v>
-      </c>
-      <c r="S33" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="T33" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="U33" s="33" t="s">
-        <v>590</v>
       </c>
       <c r="V33" s="33" t="s">
         <v>375</v>
@@ -10690,23 +10685,23 @@
         <v>149</v>
       </c>
       <c r="AF33" s="33" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG33" s="33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AH33" s="33" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AI33" s="33"/>
       <c r="AJ33" s="33" t="s">
+        <v>591</v>
+      </c>
+      <c r="AK33" s="33" t="s">
         <v>592</v>
       </c>
-      <c r="AK33" s="33" t="s">
-        <v>593</v>
-      </c>
       <c r="AL33" s="33" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AM33" s="39">
         <v>10</v>
@@ -10745,7 +10740,7 @@
         <v>43</v>
       </c>
       <c r="AY33" s="33" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AZ33" s="33" t="s">
         <v>165</v>
@@ -10757,27 +10752,27 @@
         <v>166</v>
       </c>
       <c r="BC33" s="34" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="34" spans="1:55" ht="62.1" customHeight="1">
+      <c r="A34" s="32" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="34" spans="1:55" ht="62.1" hidden="1" customHeight="1">
-      <c r="A34" s="32" t="s">
+      <c r="B34" s="33" t="s">
         <v>601</v>
       </c>
-      <c r="B34" s="33" t="s">
+      <c r="C34" s="33" t="s">
         <v>602</v>
-      </c>
-      <c r="C34" s="33" t="s">
-        <v>603</v>
       </c>
       <c r="D34" s="33" t="s">
         <v>326</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F34" s="33" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G34" s="33" t="s">
         <v>241</v>
@@ -10798,31 +10793,31 @@
         <v>149</v>
       </c>
       <c r="M34" s="33" t="s">
+        <v>604</v>
+      </c>
+      <c r="N34" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O34" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P34" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q34" s="33" t="s">
         <v>605</v>
       </c>
-      <c r="N34" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O34" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P34" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q34" s="33" t="s">
+      <c r="R34" s="33" t="s">
         <v>606</v>
       </c>
-      <c r="R34" s="33" t="s">
+      <c r="S34" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="T34" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="U34" s="33" t="s">
         <v>607</v>
-      </c>
-      <c r="S34" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="T34" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="U34" s="33" t="s">
-        <v>608</v>
       </c>
       <c r="V34" s="33" t="s">
         <v>375</v>
@@ -10855,25 +10850,25 @@
         <v>149</v>
       </c>
       <c r="AF34" s="33" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG34" s="33" t="s">
         <v>241</v>
       </c>
       <c r="AH34" s="33" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AI34" s="33" t="s">
         <v>380</v>
       </c>
       <c r="AJ34" s="33" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AK34" s="33" t="s">
         <v>382</v>
       </c>
       <c r="AL34" s="33" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AM34" s="33">
         <v>4</v>
@@ -10912,7 +10907,7 @@
         <v>43</v>
       </c>
       <c r="AY34" s="33" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AZ34" s="33" t="s">
         <v>165</v>
@@ -10924,18 +10919,18 @@
         <v>385</v>
       </c>
       <c r="BC34" s="34" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="35" spans="1:55" ht="62.1" customHeight="1">
+      <c r="A35" s="32" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="35" spans="1:55" ht="62.1" hidden="1" customHeight="1">
-      <c r="A35" s="32" t="s">
+      <c r="B35" s="33" t="s">
         <v>614</v>
       </c>
-      <c r="B35" s="33" t="s">
+      <c r="C35" s="33" t="s">
         <v>615</v>
-      </c>
-      <c r="C35" s="33" t="s">
-        <v>616</v>
       </c>
       <c r="D35" s="33" t="s">
         <v>326</v>
@@ -10944,7 +10939,7 @@
         <v>179</v>
       </c>
       <c r="F35" s="33" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G35" s="33" t="s">
         <v>179</v>
@@ -10965,31 +10960,31 @@
         <v>149</v>
       </c>
       <c r="M35" s="33" t="s">
+        <v>617</v>
+      </c>
+      <c r="N35" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O35" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P35" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q35" s="33" t="s">
         <v>618</v>
       </c>
-      <c r="N35" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O35" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P35" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q35" s="33" t="s">
+      <c r="R35" s="33" t="s">
         <v>619</v>
       </c>
-      <c r="R35" s="33" t="s">
+      <c r="S35" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="T35" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="U35" s="33" t="s">
         <v>620</v>
-      </c>
-      <c r="S35" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="T35" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="U35" s="33" t="s">
-        <v>621</v>
       </c>
       <c r="V35" s="33" t="s">
         <v>375</v>
@@ -11019,28 +11014,28 @@
         <v>180</v>
       </c>
       <c r="AE35" s="33" t="s">
+        <v>621</v>
+      </c>
+      <c r="AF35" s="33" t="s">
         <v>622</v>
-      </c>
-      <c r="AF35" s="33" t="s">
-        <v>623</v>
       </c>
       <c r="AG35" s="33" t="s">
         <v>179</v>
       </c>
       <c r="AH35" s="33" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AI35" s="33" t="s">
         <v>380</v>
       </c>
       <c r="AJ35" s="33" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AK35" s="33" t="s">
         <v>382</v>
       </c>
       <c r="AL35" s="33" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AM35" s="39">
         <v>10</v>
@@ -11070,7 +11065,7 @@
         <v>30</v>
       </c>
       <c r="AV35" s="33" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AW35" s="33" t="s">
         <v>329</v>
@@ -11079,7 +11074,7 @@
         <v>43</v>
       </c>
       <c r="AY35" s="33" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AZ35" s="33" t="s">
         <v>165</v>
@@ -11091,30 +11086,30 @@
         <v>385</v>
       </c>
       <c r="BC35" s="34" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="36" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A36" s="32" t="s">
+        <v>627</v>
+      </c>
+      <c r="B36" s="33" t="s">
         <v>628</v>
       </c>
-      <c r="B36" s="33" t="s">
+      <c r="C36" s="33" t="s">
         <v>629</v>
-      </c>
-      <c r="C36" s="33" t="s">
-        <v>630</v>
       </c>
       <c r="D36" s="33" t="s">
         <v>326</v>
       </c>
       <c r="E36" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="F36" s="33" t="s">
+        <v>630</v>
+      </c>
+      <c r="G36" s="33" t="s">
         <v>556</v>
-      </c>
-      <c r="F36" s="33" t="s">
-        <v>631</v>
-      </c>
-      <c r="G36" s="33" t="s">
-        <v>557</v>
       </c>
       <c r="H36" s="33" t="s">
         <v>285</v>
@@ -11132,31 +11127,31 @@
         <v>149</v>
       </c>
       <c r="M36" s="33" t="s">
+        <v>631</v>
+      </c>
+      <c r="N36" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O36" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P36" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q36" s="33" t="s">
         <v>632</v>
       </c>
-      <c r="N36" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O36" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P36" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q36" s="33" t="s">
+      <c r="R36" s="33" t="s">
         <v>633</v>
       </c>
-      <c r="R36" s="33" t="s">
+      <c r="S36" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="T36" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="U36" s="33" t="s">
         <v>634</v>
-      </c>
-      <c r="S36" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="T36" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="U36" s="33" t="s">
-        <v>635</v>
       </c>
       <c r="V36" s="33" t="s">
         <v>375</v>
@@ -11195,19 +11190,19 @@
         <v>299</v>
       </c>
       <c r="AH36" s="33" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AI36" s="33" t="s">
         <v>380</v>
       </c>
       <c r="AJ36" s="33" t="s">
+        <v>636</v>
+      </c>
+      <c r="AK36" s="33" t="s">
         <v>637</v>
       </c>
-      <c r="AK36" s="33" t="s">
+      <c r="AL36" s="33" t="s">
         <v>638</v>
-      </c>
-      <c r="AL36" s="33" t="s">
-        <v>639</v>
       </c>
       <c r="AM36" s="33">
         <v>4</v>
@@ -11246,7 +11241,7 @@
         <v>43</v>
       </c>
       <c r="AY36" s="33" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AZ36" s="33" t="s">
         <v>165</v>
@@ -11258,18 +11253,18 @@
         <v>166</v>
       </c>
       <c r="BC36" s="34" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="37" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A37" s="32" t="s">
+        <v>639</v>
+      </c>
+      <c r="B37" s="33" t="s">
         <v>640</v>
       </c>
-      <c r="B37" s="33" t="s">
+      <c r="C37" s="33" t="s">
         <v>641</v>
-      </c>
-      <c r="C37" s="33" t="s">
-        <v>642</v>
       </c>
       <c r="D37" s="33" t="s">
         <v>326</v>
@@ -11278,7 +11273,7 @@
         <v>270</v>
       </c>
       <c r="F37" s="33" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G37" s="33" t="s">
         <v>272</v>
@@ -11299,31 +11294,31 @@
         <v>149</v>
       </c>
       <c r="M37" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="N37" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O37" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P37" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q37" s="33" t="s">
         <v>644</v>
       </c>
-      <c r="N37" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O37" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P37" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q37" s="33" t="s">
+      <c r="R37" s="33" t="s">
         <v>645</v>
       </c>
-      <c r="R37" s="33" t="s">
+      <c r="S37" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="T37" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="U37" s="33" t="s">
         <v>646</v>
-      </c>
-      <c r="S37" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="T37" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="U37" s="33" t="s">
-        <v>647</v>
       </c>
       <c r="V37" s="33" t="s">
         <v>375</v>
@@ -11356,25 +11351,25 @@
         <v>149</v>
       </c>
       <c r="AF37" s="33" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AG37" s="33" t="s">
         <v>272</v>
       </c>
       <c r="AH37" s="33" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AI37" s="33" t="s">
         <v>380</v>
       </c>
       <c r="AJ37" s="33" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AK37" s="33" t="s">
         <v>382</v>
       </c>
       <c r="AL37" s="33" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AM37" s="33">
         <v>10</v>
@@ -11413,7 +11408,7 @@
         <v>43</v>
       </c>
       <c r="AY37" s="33" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AZ37" s="33" t="s">
         <v>165</v>
@@ -11425,30 +11420,30 @@
         <v>166</v>
       </c>
       <c r="BC37" s="34" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="38" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A38" s="32" t="s">
+        <v>652</v>
+      </c>
+      <c r="B38" s="33" t="s">
         <v>653</v>
       </c>
-      <c r="B38" s="33" t="s">
+      <c r="C38" s="33" t="s">
         <v>654</v>
-      </c>
-      <c r="C38" s="33" t="s">
-        <v>655</v>
       </c>
       <c r="D38" s="33" t="s">
         <v>326</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F38" s="33" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G38" s="33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H38" s="33" t="s">
         <v>142</v>
@@ -11466,7 +11461,7 @@
         <v>149</v>
       </c>
       <c r="M38" s="33" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="N38" s="33" t="s">
         <v>43</v>
@@ -11478,11 +11473,11 @@
         <v>149</v>
       </c>
       <c r="Q38" s="33" t="s">
+        <v>656</v>
+      </c>
+      <c r="R38" s="33" t="s">
         <v>657</v>
       </c>
-      <c r="R38" s="33" t="s">
-        <v>658</v>
-      </c>
       <c r="S38" s="33" t="s">
         <v>149</v>
       </c>
@@ -11490,7 +11485,7 @@
         <v>149</v>
       </c>
       <c r="U38" s="33" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="V38" s="33" t="s">
         <v>375</v>
@@ -11523,25 +11518,25 @@
         <v>149</v>
       </c>
       <c r="AF38" s="33" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG38" s="33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AH38" s="33" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AI38" s="33" t="s">
         <v>380</v>
       </c>
       <c r="AJ38" s="33" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AK38" s="33" t="s">
         <v>382</v>
       </c>
       <c r="AL38" s="33" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AM38" s="39">
         <v>10</v>
@@ -11562,7 +11557,7 @@
         <v>1.5</v>
       </c>
       <c r="AS38" s="33" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AT38" s="33">
         <v>0.65</v>
@@ -11571,7 +11566,7 @@
         <v>30</v>
       </c>
       <c r="AV38" s="33" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AW38" s="33" t="s">
         <v>329</v>
@@ -11580,7 +11575,7 @@
         <v>43</v>
       </c>
       <c r="AY38" s="33" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AZ38" s="33" t="s">
         <v>165</v>
@@ -11592,18 +11587,18 @@
         <v>166</v>
       </c>
       <c r="BC38" s="34" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="39" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="39" spans="1:55" ht="62.1" customHeight="1">
       <c r="A39" s="32" t="s">
+        <v>663</v>
+      </c>
+      <c r="B39" s="33" t="s">
         <v>664</v>
       </c>
-      <c r="B39" s="33" t="s">
+      <c r="C39" s="33" t="s">
         <v>665</v>
-      </c>
-      <c r="C39" s="33" t="s">
-        <v>666</v>
       </c>
       <c r="D39" s="33" t="s">
         <v>326</v>
@@ -11612,10 +11607,10 @@
         <v>270</v>
       </c>
       <c r="F39" s="33" t="s">
+        <v>666</v>
+      </c>
+      <c r="G39" s="33" t="s">
         <v>667</v>
-      </c>
-      <c r="G39" s="33" t="s">
-        <v>668</v>
       </c>
       <c r="H39" s="33" t="s">
         <v>285</v>
@@ -11633,31 +11628,31 @@
         <v>149</v>
       </c>
       <c r="M39" s="33" t="s">
+        <v>668</v>
+      </c>
+      <c r="N39" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O39" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P39" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q39" s="33" t="s">
         <v>669</v>
       </c>
-      <c r="N39" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O39" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P39" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q39" s="33" t="s">
+      <c r="R39" s="33" t="s">
         <v>670</v>
       </c>
-      <c r="R39" s="33" t="s">
+      <c r="S39" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="T39" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="U39" s="33" t="s">
         <v>671</v>
-      </c>
-      <c r="S39" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="T39" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="U39" s="33" t="s">
-        <v>672</v>
       </c>
       <c r="V39" s="33" t="s">
         <v>375</v>
@@ -11687,28 +11682,28 @@
         <v>229</v>
       </c>
       <c r="AE39" s="33" t="s">
+        <v>672</v>
+      </c>
+      <c r="AF39" s="33" t="s">
         <v>673</v>
-      </c>
-      <c r="AF39" s="33" t="s">
-        <v>674</v>
       </c>
       <c r="AG39" s="33" t="s">
         <v>222</v>
       </c>
       <c r="AH39" s="33" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AI39" s="33" t="s">
         <v>380</v>
       </c>
       <c r="AJ39" s="33" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AK39" s="33" t="s">
         <v>382</v>
       </c>
       <c r="AL39" s="33" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AM39" s="39">
         <v>10</v>
@@ -11747,7 +11742,7 @@
         <v>43</v>
       </c>
       <c r="AY39" s="33" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AZ39" s="33" t="s">
         <v>165</v>
@@ -11756,21 +11751,21 @@
         <v>67</v>
       </c>
       <c r="BB39" s="33" t="s">
-        <v>385</v>
+        <v>166</v>
       </c>
       <c r="BC39" s="34" t="s">
-        <v>679</v>
+        <v>914</v>
       </c>
     </row>
     <row r="40" spans="1:55" ht="62.1" customHeight="1">
       <c r="A40" s="32" t="s">
+        <v>678</v>
+      </c>
+      <c r="B40" s="33" t="s">
+        <v>679</v>
+      </c>
+      <c r="C40" s="33" t="s">
         <v>680</v>
-      </c>
-      <c r="B40" s="33" t="s">
-        <v>681</v>
-      </c>
-      <c r="C40" s="33" t="s">
-        <v>682</v>
       </c>
       <c r="D40" s="33" t="s">
         <v>326</v>
@@ -11779,7 +11774,7 @@
         <v>432</v>
       </c>
       <c r="F40" s="33" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="G40" s="33" t="s">
         <v>434</v>
@@ -11800,31 +11795,31 @@
         <v>149</v>
       </c>
       <c r="M40" s="33" t="s">
+        <v>682</v>
+      </c>
+      <c r="N40" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O40" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P40" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q40" s="33" t="s">
+        <v>683</v>
+      </c>
+      <c r="R40" s="33" t="s">
         <v>684</v>
       </c>
-      <c r="N40" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="O40" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P40" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q40" s="33" t="s">
+      <c r="S40" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="T40" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="U40" s="33" t="s">
         <v>685</v>
-      </c>
-      <c r="R40" s="33" t="s">
-        <v>686</v>
-      </c>
-      <c r="S40" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="T40" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="U40" s="33" t="s">
-        <v>687</v>
       </c>
       <c r="V40" s="33" t="s">
         <v>375</v>
@@ -11863,19 +11858,19 @@
         <v>434</v>
       </c>
       <c r="AH40" s="33" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="AI40" s="33" t="s">
         <v>380</v>
       </c>
       <c r="AJ40" s="33" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="AK40" s="33" t="s">
         <v>382</v>
       </c>
       <c r="AL40" s="33" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="AM40" s="39">
         <v>10</v>
@@ -11914,7 +11909,7 @@
         <v>43</v>
       </c>
       <c r="AY40" s="33" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="AZ40" s="33" t="s">
         <v>165</v>
@@ -11923,19 +11918,19 @@
         <v>67</v>
       </c>
       <c r="BB40" s="33" t="s">
-        <v>385</v>
+        <v>166</v>
       </c>
       <c r="BC40" s="34" t="s">
-        <v>692</v>
+        <v>915</v>
       </c>
     </row>
     <row r="41" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A41" s="32"/>
       <c r="B41" s="35" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D41" s="33" t="s">
         <v>326</v>
@@ -11944,7 +11939,7 @@
         <v>179</v>
       </c>
       <c r="F41" s="35" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="G41" s="33" t="s">
         <v>179</v>
@@ -11959,21 +11954,21 @@
       <c r="K41" s="33"/>
       <c r="L41" s="33"/>
       <c r="M41" s="33" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="N41" s="33"/>
       <c r="O41" s="33"/>
       <c r="P41" s="33"/>
       <c r="Q41" s="33" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="R41" s="33" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S41" s="33"/>
       <c r="T41" s="33"/>
       <c r="U41" s="33" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="V41" s="33" t="s">
         <v>375</v>
@@ -12001,24 +11996,24 @@
         <v>210</v>
       </c>
       <c r="AE41" s="33" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AF41" s="33" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="AG41" s="33" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="AH41" s="33"/>
       <c r="AI41" s="37"/>
       <c r="AJ41" s="33" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="AK41" s="33" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="AL41" s="33" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="AM41" s="33">
         <v>4</v>
@@ -12055,7 +12050,7 @@
         <v>248</v>
       </c>
       <c r="AY41" s="33" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="AZ41" s="33" t="s">
         <v>165</v>
@@ -12067,16 +12062,16 @@
         <v>166</v>
       </c>
       <c r="BC41" s="34" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="42" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A42" s="32"/>
       <c r="B42" s="35" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D42" s="33" t="s">
         <v>326</v>
@@ -12085,7 +12080,7 @@
         <v>239</v>
       </c>
       <c r="F42" s="35" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="G42" s="33" t="s">
         <v>241</v>
@@ -12100,7 +12095,7 @@
       <c r="K42" s="35"/>
       <c r="L42" s="33"/>
       <c r="M42" s="35" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="N42" s="35" t="s">
         <v>43</v>
@@ -12122,7 +12117,7 @@
         <v>247</v>
       </c>
       <c r="U42" s="35" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="V42" s="33" t="s">
         <v>40</v>
@@ -12165,7 +12160,7 @@
       </c>
       <c r="AI42" s="33"/>
       <c r="AJ42" s="35" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="AK42" s="33" t="s">
         <v>250</v>
@@ -12210,7 +12205,7 @@
         <v>40</v>
       </c>
       <c r="AY42" s="33" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="AZ42" s="33" t="s">
         <v>34</v>
@@ -12227,13 +12222,13 @@
     </row>
     <row r="43" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A43" s="41" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B43" s="42" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C43" s="42" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D43" s="42" t="s">
         <v>139</v>
@@ -12242,7 +12237,7 @@
         <v>432</v>
       </c>
       <c r="F43" s="42" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="G43" s="42" t="s">
         <v>434</v>
@@ -12254,31 +12249,31 @@
         <v>143</v>
       </c>
       <c r="J43" s="42" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="K43" s="42" t="s">
         <v>242</v>
       </c>
       <c r="L43" s="42" t="s">
+        <v>716</v>
+      </c>
+      <c r="M43" s="42" t="s">
+        <v>717</v>
+      </c>
+      <c r="N43" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="O43" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="P43" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q43" s="42" t="s">
+        <v>718</v>
+      </c>
+      <c r="R43" s="42" t="s">
         <v>719</v>
-      </c>
-      <c r="M43" s="42" t="s">
-        <v>720</v>
-      </c>
-      <c r="N43" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="O43" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="P43" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q43" s="42" t="s">
-        <v>721</v>
-      </c>
-      <c r="R43" s="42" t="s">
-        <v>722</v>
       </c>
       <c r="S43" s="42" t="s">
         <v>149</v>
@@ -12287,7 +12282,7 @@
         <v>213</v>
       </c>
       <c r="U43" s="42" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="V43" s="42" t="s">
         <v>40</v>
@@ -12314,31 +12309,31 @@
         <v>149</v>
       </c>
       <c r="AD43" s="42" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="AE43" s="42" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="AF43" s="42" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="AG43" s="42" t="s">
         <v>434</v>
       </c>
       <c r="AH43" s="42" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="AI43" s="42" t="s">
         <v>329</v>
       </c>
       <c r="AJ43" s="42" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="AK43" s="42" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="AL43" s="42" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="AM43" s="42">
         <v>6</v>
@@ -12374,10 +12369,10 @@
         <v>329</v>
       </c>
       <c r="AX43" s="42" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="AY43" s="42" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="AZ43" s="42" t="s">
         <v>165</v>
@@ -12389,18 +12384,18 @@
         <v>166</v>
       </c>
       <c r="BC43" s="43" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="44" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A44" s="41" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B44" s="42" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C44" s="42" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D44" s="42" t="s">
         <v>139</v>
@@ -12409,7 +12404,7 @@
         <v>432</v>
       </c>
       <c r="F44" s="42" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="G44" s="42" t="s">
         <v>434</v>
@@ -12421,40 +12416,40 @@
         <v>143</v>
       </c>
       <c r="J44" s="42" t="s">
+        <v>735</v>
+      </c>
+      <c r="K44" s="42" t="s">
+        <v>736</v>
+      </c>
+      <c r="L44" s="42" t="s">
+        <v>737</v>
+      </c>
+      <c r="M44" s="42" t="s">
         <v>738</v>
       </c>
-      <c r="K44" s="42" t="s">
+      <c r="N44" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="O44" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="P44" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q44" s="42" t="s">
         <v>739</v>
       </c>
-      <c r="L44" s="42" t="s">
+      <c r="R44" s="42" t="s">
         <v>740</v>
       </c>
-      <c r="M44" s="42" t="s">
+      <c r="S44" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="T44" s="42" t="s">
         <v>741</v>
       </c>
-      <c r="N44" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="O44" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="P44" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q44" s="42" t="s">
+      <c r="U44" s="42" t="s">
         <v>742</v>
-      </c>
-      <c r="R44" s="42" t="s">
-        <v>743</v>
-      </c>
-      <c r="S44" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="T44" s="42" t="s">
-        <v>744</v>
-      </c>
-      <c r="U44" s="42" t="s">
-        <v>745</v>
       </c>
       <c r="V44" s="42" t="s">
         <v>40</v>
@@ -12481,31 +12476,31 @@
         <v>149</v>
       </c>
       <c r="AD44" s="42" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="AE44" s="42" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="AF44" s="42" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="AG44" s="42" t="s">
         <v>434</v>
       </c>
       <c r="AH44" s="42" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="AI44" s="42" t="s">
         <v>329</v>
       </c>
       <c r="AJ44" s="42" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="AK44" s="42" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="AL44" s="42" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="AM44" s="42">
         <v>4</v>
@@ -12541,10 +12536,10 @@
         <v>329</v>
       </c>
       <c r="AX44" s="42" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="AY44" s="42" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="AZ44" s="42" t="s">
         <v>165</v>
@@ -12556,18 +12551,18 @@
         <v>166</v>
       </c>
       <c r="BC44" s="43" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="45" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A45" s="41" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B45" s="42" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="C45" s="42" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D45" s="42" t="s">
         <v>139</v>
@@ -12576,7 +12571,7 @@
         <v>432</v>
       </c>
       <c r="F45" s="42" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="G45" s="42" t="s">
         <v>434</v>
@@ -12588,40 +12583,40 @@
         <v>143</v>
       </c>
       <c r="J45" s="42" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="K45" s="42" t="s">
         <v>242</v>
       </c>
       <c r="L45" s="42" t="s">
+        <v>753</v>
+      </c>
+      <c r="M45" s="42" t="s">
+        <v>754</v>
+      </c>
+      <c r="N45" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="O45" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="P45" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q45" s="42" t="s">
+        <v>755</v>
+      </c>
+      <c r="R45" s="42" t="s">
         <v>756</v>
       </c>
-      <c r="M45" s="42" t="s">
+      <c r="S45" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="T45" s="42" t="s">
         <v>757</v>
       </c>
-      <c r="N45" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="O45" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="P45" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q45" s="42" t="s">
+      <c r="U45" s="42" t="s">
         <v>758</v>
-      </c>
-      <c r="R45" s="42" t="s">
-        <v>759</v>
-      </c>
-      <c r="S45" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="T45" s="42" t="s">
-        <v>760</v>
-      </c>
-      <c r="U45" s="42" t="s">
-        <v>761</v>
       </c>
       <c r="V45" s="42" t="s">
         <v>40</v>
@@ -12648,31 +12643,31 @@
         <v>149</v>
       </c>
       <c r="AD45" s="42" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="AE45" s="42" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="AF45" s="42" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="AG45" s="42" t="s">
         <v>434</v>
       </c>
       <c r="AH45" s="42" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="AI45" s="42" t="s">
         <v>329</v>
       </c>
       <c r="AJ45" s="42" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="AK45" s="42" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="AL45" s="42" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="AM45" s="42">
         <v>3</v>
@@ -12708,10 +12703,10 @@
         <v>329</v>
       </c>
       <c r="AX45" s="42" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="AY45" s="42" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="AZ45" s="42" t="s">
         <v>165</v>
@@ -12723,30 +12718,30 @@
         <v>166</v>
       </c>
       <c r="BC45" s="43" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="46" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A46" s="32" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B46" s="35" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="D46" s="40" t="s">
         <v>166</v>
       </c>
       <c r="E46" s="33" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F46" s="35" t="s">
         <v>58</v>
       </c>
       <c r="G46" s="33" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="H46" s="35" t="s">
         <v>41</v>
@@ -12756,7 +12751,7 @@
       </c>
       <c r="J46" s="35"/>
       <c r="K46" s="35" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="L46" s="33"/>
       <c r="M46" s="35"/>
@@ -12767,14 +12762,14 @@
         <v>40</v>
       </c>
       <c r="R46" s="33" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="S46" s="33"/>
       <c r="T46" s="33" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="U46" s="35" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="V46" s="33" t="s">
         <v>40</v>
@@ -12801,13 +12796,13 @@
       </c>
       <c r="AE46" s="33"/>
       <c r="AF46" s="33" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="AG46" s="33"/>
       <c r="AH46" s="33"/>
       <c r="AI46" s="33"/>
       <c r="AJ46" s="35" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="AK46" s="33"/>
       <c r="AL46" s="33"/>
@@ -12841,10 +12836,10 @@
         <v>43</v>
       </c>
       <c r="AX46" s="33" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="AY46" s="33" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="AZ46" s="33" t="s">
         <v>34</v>
@@ -12859,25 +12854,25 @@
     </row>
     <row r="47" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A47" s="32" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B47" s="35" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="D47" s="40" t="s">
         <v>166</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F47" s="35" t="s">
         <v>58</v>
       </c>
       <c r="G47" s="33" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="H47" s="35" t="s">
         <v>41</v>
@@ -12887,7 +12882,7 @@
       </c>
       <c r="J47" s="35"/>
       <c r="K47" s="35" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="L47" s="33"/>
       <c r="M47" s="35"/>
@@ -12898,14 +12893,14 @@
         <v>40</v>
       </c>
       <c r="R47" s="33" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="S47" s="33"/>
       <c r="T47" s="33" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="U47" s="35" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="V47" s="33" t="s">
         <v>40</v>
@@ -12932,13 +12927,13 @@
       </c>
       <c r="AE47" s="33"/>
       <c r="AF47" s="33" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="AG47" s="33"/>
       <c r="AH47" s="33"/>
       <c r="AI47" s="33"/>
       <c r="AJ47" s="35" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="AK47" s="33"/>
       <c r="AL47" s="33"/>
@@ -12972,10 +12967,10 @@
         <v>43</v>
       </c>
       <c r="AX47" s="33" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="AY47" s="33" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="AZ47" s="33" t="s">
         <v>34</v>
@@ -12990,25 +12985,25 @@
     </row>
     <row r="48" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A48" s="32" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B48" s="35" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="D48" s="40" t="s">
         <v>166</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="F48" s="35" t="s">
         <v>58</v>
       </c>
       <c r="G48" s="33" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="H48" s="35" t="s">
         <v>41</v>
@@ -13018,7 +13013,7 @@
       </c>
       <c r="J48" s="35"/>
       <c r="K48" s="35" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="L48" s="33"/>
       <c r="M48" s="35"/>
@@ -13029,11 +13024,11 @@
         <v>40</v>
       </c>
       <c r="R48" s="33" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="S48" s="33"/>
       <c r="T48" s="33" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="U48" s="35" t="s">
         <v>51</v>
@@ -13069,7 +13064,7 @@
       <c r="AH48" s="33"/>
       <c r="AI48" s="33"/>
       <c r="AJ48" s="35" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="AK48" s="33"/>
       <c r="AL48" s="33"/>
@@ -13103,10 +13098,10 @@
         <v>43</v>
       </c>
       <c r="AX48" s="33" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="AY48" s="33" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="AZ48" s="33" t="s">
         <v>34</v>
@@ -13121,25 +13116,25 @@
     </row>
     <row r="49" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A49" s="32" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B49" s="35" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D49" s="40" t="s">
         <v>166</v>
       </c>
       <c r="E49" s="33" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="F49" s="35" t="s">
         <v>58</v>
       </c>
       <c r="G49" s="33" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="H49" s="35" t="s">
         <v>41</v>
@@ -13149,7 +13144,7 @@
       </c>
       <c r="J49" s="35"/>
       <c r="K49" s="35" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="L49" s="33"/>
       <c r="M49" s="35"/>
@@ -13160,11 +13155,11 @@
         <v>40</v>
       </c>
       <c r="R49" s="33" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="S49" s="33"/>
       <c r="T49" s="33" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="U49" s="35" t="s">
         <v>51</v>
@@ -13200,7 +13195,7 @@
       <c r="AH49" s="33"/>
       <c r="AI49" s="33"/>
       <c r="AJ49" s="35" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="AK49" s="33"/>
       <c r="AL49" s="33"/>
@@ -13234,10 +13229,10 @@
         <v>43</v>
       </c>
       <c r="AX49" s="33" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="AY49" s="33" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="AZ49" s="33" t="s">
         <v>34</v>
@@ -13253,55 +13248,55 @@
     <row r="50" spans="1:55" ht="62.1" hidden="1" customHeight="1">
       <c r="A50" s="32"/>
       <c r="B50" s="35" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="C50" s="35" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D50" s="33" t="s">
         <v>326</v>
       </c>
       <c r="E50" s="33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F50" s="35" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="G50" s="33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H50" s="35" t="s">
         <v>142</v>
       </c>
       <c r="I50" s="33" t="s">
+        <v>585</v>
+      </c>
+      <c r="J50" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="K50" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="L50" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="M50" s="35" t="s">
         <v>586</v>
       </c>
-      <c r="J50" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="K50" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="L50" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="M50" s="35" t="s">
+      <c r="N50" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="O50" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="P50" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q50" s="33" t="s">
         <v>587</v>
       </c>
-      <c r="N50" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="O50" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P50" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q50" s="33" t="s">
-        <v>588</v>
-      </c>
       <c r="R50" s="33" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="S50" s="33" t="s">
         <v>149</v>
@@ -13310,7 +13305,7 @@
         <v>149</v>
       </c>
       <c r="U50" s="35" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="V50" s="33" t="s">
         <v>375</v>
@@ -13343,23 +13338,23 @@
         <v>149</v>
       </c>
       <c r="AF50" s="33" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG50" s="33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AH50" s="33" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AI50" s="33"/>
       <c r="AJ50" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="AK50" s="33" t="s">
         <v>592</v>
       </c>
-      <c r="AK50" s="33" t="s">
-        <v>593</v>
-      </c>
       <c r="AL50" s="33" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="AM50" s="39">
         <v>10</v>
@@ -13398,7 +13393,7 @@
         <v>43</v>
       </c>
       <c r="AY50" s="33" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AZ50" s="33" t="s">
         <v>165</v>
@@ -13410,7 +13405,7 @@
         <v>166</v>
       </c>
       <c r="BC50" s="36" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
     </row>
     <row r="51" spans="1:55" ht="62.1" hidden="1" customHeight="1">
@@ -13584,13 +13579,13 @@
       <c r="BB53" s="33"/>
       <c r="BC53" s="36"/>
     </row>
-    <row r="54" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+    <row r="54" spans="1:55" ht="62.1" customHeight="1">
       <c r="A54" s="32"/>
       <c r="B54" s="35" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C54" s="35" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="D54" s="33" t="s">
         <v>326</v>
@@ -13599,10 +13594,10 @@
         <v>417</v>
       </c>
       <c r="F54" s="35" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="G54" s="33" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="H54" s="35" t="s">
         <v>142</v>
@@ -13620,7 +13615,7 @@
         <v>149</v>
       </c>
       <c r="M54" s="35" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="N54" s="35" t="s">
         <v>43</v>
@@ -13632,10 +13627,10 @@
         <v>149</v>
       </c>
       <c r="Q54" s="33" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="R54" s="33" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="S54" s="33" t="s">
         <v>149</v>
@@ -13674,7 +13669,7 @@
         <v>229</v>
       </c>
       <c r="AE54" s="33" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="AF54" s="33" t="s">
         <v>424</v>
@@ -13689,10 +13684,10 @@
         <v>380</v>
       </c>
       <c r="AJ54" s="35" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="AK54" s="33" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="AL54" s="33" t="s">
         <v>427</v>
@@ -13746,16 +13741,16 @@
         <v>385</v>
       </c>
       <c r="BC54" s="36" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="55" spans="1:55" ht="62.1" hidden="1" customHeight="1">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="55" spans="1:55" ht="62.1" customHeight="1">
       <c r="A55" s="32"/>
       <c r="B55" s="33" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="C55" s="33" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="D55" s="33" t="s">
         <v>326</v>
@@ -13764,10 +13759,10 @@
         <v>417</v>
       </c>
       <c r="F55" s="33" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="G55" s="33" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="H55" s="33" t="s">
         <v>142</v>
@@ -13785,7 +13780,7 @@
         <v>149</v>
       </c>
       <c r="M55" s="33" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="N55" s="33" t="s">
         <v>43</v>
@@ -13797,10 +13792,10 @@
         <v>149</v>
       </c>
       <c r="Q55" s="33" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="R55" s="33" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="S55" s="33" t="s">
         <v>149</v>
@@ -13839,7 +13834,7 @@
         <v>229</v>
       </c>
       <c r="AE55" s="33" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="AF55" s="33" t="s">
         <v>424</v>
@@ -13854,10 +13849,10 @@
         <v>380</v>
       </c>
       <c r="AJ55" s="33" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="AK55" s="33" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="AL55" s="33" t="s">
         <v>427</v>
@@ -13911,25 +13906,25 @@
         <v>385</v>
       </c>
       <c r="BC55" s="34" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
     </row>
     <row r="56" spans="1:55" ht="62.1" customHeight="1">
       <c r="A56" s="32"/>
       <c r="B56" s="33" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="C56" s="33" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="D56" s="33" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="E56" s="33" t="s">
         <v>432</v>
       </c>
       <c r="F56" s="33" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="G56" s="33" t="s">
         <v>434</v>
@@ -13942,11 +13937,11 @@
       </c>
       <c r="J56" s="33"/>
       <c r="K56" s="33" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="L56" s="33"/>
       <c r="M56" s="33" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="N56" s="33" t="s">
         <v>43</v>
@@ -13954,17 +13949,17 @@
       <c r="O56" s="33"/>
       <c r="P56" s="33"/>
       <c r="Q56" s="33" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="R56" s="33" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="S56" s="33"/>
       <c r="T56" s="33" t="s">
         <v>213</v>
       </c>
       <c r="U56" s="33" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="V56" s="33" t="s">
         <v>40</v>
@@ -13991,17 +13986,17 @@
       <c r="AD56" s="33"/>
       <c r="AE56" s="33"/>
       <c r="AF56" s="33" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="AG56" s="33" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="AH56" s="33" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="AI56" s="33"/>
       <c r="AJ56" s="33" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="AK56" s="33"/>
       <c r="AL56" s="33"/>
@@ -14024,7 +14019,7 @@
         <v>0.8</v>
       </c>
       <c r="AS56" s="33" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="AT56" s="39">
         <v>0.55000000000000004</v>
@@ -14036,30 +14031,30 @@
         <v>0.08</v>
       </c>
       <c r="AW56" s="33" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="AX56" s="33" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="AY56" s="33"/>
       <c r="AZ56" s="33"/>
       <c r="BA56" s="33"/>
       <c r="BB56" s="33" t="s">
-        <v>385</v>
+        <v>166</v>
       </c>
       <c r="BC56" s="34" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="57" spans="1:55" ht="63" hidden="1" customHeight="1">
       <c r="A57" s="41" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="B57" s="42" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C57" s="42" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="D57" s="42" t="s">
         <v>139</v>
@@ -14068,7 +14063,7 @@
         <v>432</v>
       </c>
       <c r="F57" s="42" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="G57" s="42" t="s">
         <v>434</v>
@@ -14080,31 +14075,31 @@
         <v>143</v>
       </c>
       <c r="J57" s="42" t="s">
+        <v>813</v>
+      </c>
+      <c r="K57" s="42" t="s">
+        <v>814</v>
+      </c>
+      <c r="L57" s="42" t="s">
+        <v>814</v>
+      </c>
+      <c r="M57" s="42" t="s">
+        <v>815</v>
+      </c>
+      <c r="N57" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="O57" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="P57" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q57" s="42" t="s">
         <v>816</v>
       </c>
-      <c r="K57" s="42" t="s">
+      <c r="R57" s="42" t="s">
         <v>817</v>
-      </c>
-      <c r="L57" s="42" t="s">
-        <v>817</v>
-      </c>
-      <c r="M57" s="42" t="s">
-        <v>818</v>
-      </c>
-      <c r="N57" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="O57" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="P57" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q57" s="42" t="s">
-        <v>819</v>
-      </c>
-      <c r="R57" s="42" t="s">
-        <v>820</v>
       </c>
       <c r="S57" s="42" t="s">
         <v>149</v>
@@ -14113,7 +14108,7 @@
         <v>153</v>
       </c>
       <c r="U57" s="42" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="V57" s="42" t="s">
         <v>40</v>
@@ -14140,31 +14135,31 @@
         <v>149</v>
       </c>
       <c r="AD57" s="42" t="s">
+        <v>819</v>
+      </c>
+      <c r="AE57" s="42" t="s">
+        <v>812</v>
+      </c>
+      <c r="AF57" s="42" t="s">
+        <v>820</v>
+      </c>
+      <c r="AG57" s="42" t="s">
+        <v>821</v>
+      </c>
+      <c r="AH57" s="42" t="s">
         <v>822</v>
-      </c>
-      <c r="AE57" s="42" t="s">
-        <v>815</v>
-      </c>
-      <c r="AF57" s="42" t="s">
-        <v>823</v>
-      </c>
-      <c r="AG57" s="42" t="s">
-        <v>824</v>
-      </c>
-      <c r="AH57" s="42" t="s">
-        <v>825</v>
       </c>
       <c r="AI57" s="42" t="s">
         <v>329</v>
       </c>
       <c r="AJ57" s="42" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="AK57" s="42" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="AL57" s="42" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="AM57" s="42">
         <v>2</v>
@@ -14200,10 +14195,10 @@
         <v>329</v>
       </c>
       <c r="AX57" s="42" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="AY57" s="42" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="AZ57" s="42" t="s">
         <v>165</v>
@@ -14215,7 +14210,7 @@
         <v>166</v>
       </c>
       <c r="BC57" s="43" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
     </row>
   </sheetData>
@@ -14255,16 +14250,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="11" t="s">
+        <v>827</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>828</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>830</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>831</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>832</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="27.95" customHeight="1">
@@ -14272,13 +14267,13 @@
         <v>137</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="27.95" customHeight="1">
@@ -14286,13 +14281,13 @@
         <v>137</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>145</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="27.95" customHeight="1">
@@ -14300,13 +14295,13 @@
         <v>137</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>146</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="27.95" customHeight="1">
@@ -14314,13 +14309,13 @@
         <v>137</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>148</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.95" customHeight="1">
@@ -14328,13 +14323,13 @@
         <v>137</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.95" customHeight="1">
@@ -14342,13 +14337,13 @@
         <v>168</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>172</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27.95" customHeight="1">
@@ -14356,13 +14351,13 @@
         <v>168</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>173</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="27.95" customHeight="1">
@@ -14370,13 +14365,13 @@
         <v>168</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>146</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="27.95" customHeight="1">
@@ -14384,13 +14379,13 @@
         <v>168</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>175</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="27.95" customHeight="1">
@@ -14398,13 +14393,13 @@
         <v>168</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="27.95" customHeight="1">
@@ -14412,13 +14407,13 @@
         <v>77</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>190</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27.95" customHeight="1">
@@ -14426,13 +14421,13 @@
         <v>77</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>191</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27.95" customHeight="1">
@@ -14440,13 +14435,13 @@
         <v>77</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>192</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="27.95" customHeight="1">
@@ -14454,13 +14449,13 @@
         <v>77</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="27.95" customHeight="1">
@@ -14468,13 +14463,13 @@
         <v>77</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="27.95" customHeight="1">
@@ -14482,13 +14477,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>206</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="27.95" customHeight="1">
@@ -14496,13 +14491,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>207</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="27.95" customHeight="1">
@@ -14510,13 +14505,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>208</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="27.95" customHeight="1">
@@ -14524,13 +14519,13 @@
         <v>74</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="27.95" customHeight="1">
@@ -14538,13 +14533,13 @@
         <v>74</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="27.95" customHeight="1">
@@ -14552,13 +14547,13 @@
         <v>68</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>225</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="27.95" customHeight="1">
@@ -14566,13 +14561,13 @@
         <v>68</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>225</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="27.95" customHeight="1">
@@ -14580,13 +14575,13 @@
         <v>68</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="27.95" customHeight="1">
@@ -14594,13 +14589,13 @@
         <v>68</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="27.95" customHeight="1">
@@ -14608,13 +14603,13 @@
         <v>68</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="27.95" customHeight="1">
@@ -14622,13 +14617,13 @@
         <v>237</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="27.95" customHeight="1">
@@ -14636,13 +14631,13 @@
         <v>237</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>242</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="27.95" customHeight="1">
@@ -14650,13 +14645,13 @@
         <v>237</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>146</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="27.95" customHeight="1">
@@ -14664,13 +14659,13 @@
         <v>237</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>148</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="27.95" customHeight="1">
@@ -14678,13 +14673,13 @@
         <v>237</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>244</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="27.95" customHeight="1">
@@ -14692,13 +14687,13 @@
         <v>254</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>258</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="27.95" customHeight="1">
@@ -14706,13 +14701,13 @@
         <v>254</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>173</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="27.95" customHeight="1">
@@ -14720,13 +14715,13 @@
         <v>254</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="27.95" customHeight="1">
@@ -14734,13 +14729,13 @@
         <v>254</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="27.95" customHeight="1">
@@ -14748,13 +14743,13 @@
         <v>254</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>259</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="27.95" customHeight="1">
@@ -14762,13 +14757,13 @@
         <v>268</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>273</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="27.95" customHeight="1">
@@ -14776,13 +14771,13 @@
         <v>268</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>273</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="27.95" customHeight="1">
@@ -14790,13 +14785,13 @@
         <v>268</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="27.95" customHeight="1">
@@ -14804,13 +14799,13 @@
         <v>268</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>274</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="27.95" customHeight="1">
@@ -14818,13 +14813,13 @@
         <v>268</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>275</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="27.95" customHeight="1">
@@ -14832,13 +14827,13 @@
         <v>71</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>286</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="27.95" customHeight="1">
@@ -14846,13 +14841,13 @@
         <v>71</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>273</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="27.95" customHeight="1">
@@ -14860,13 +14855,13 @@
         <v>71</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="27.95" customHeight="1">
@@ -14874,13 +14869,13 @@
         <v>71</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>287</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="27.95" customHeight="1">
@@ -14888,13 +14883,13 @@
         <v>71</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="27.95" customHeight="1">
@@ -14902,13 +14897,13 @@
         <v>296</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>300</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="27.95" customHeight="1">
@@ -14916,13 +14911,13 @@
         <v>296</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>301</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="27.95" customHeight="1">
@@ -14930,13 +14925,13 @@
         <v>296</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>149</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="27.95" customHeight="1">
@@ -14944,13 +14939,13 @@
         <v>296</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>175</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="27.95" customHeight="1">
@@ -14958,13 +14953,13 @@
         <v>296</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>302</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="27.95" customHeight="1">
@@ -14972,13 +14967,13 @@
         <v>311</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="27.95" customHeight="1">
@@ -14986,13 +14981,13 @@
         <v>311</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>314</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="27.95" customHeight="1">
@@ -15000,13 +14995,13 @@
         <v>311</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C54" s="15" t="s">
         <v>315</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="27.95" customHeight="1">
@@ -15014,13 +15009,13 @@
         <v>311</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>316</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="27.95" customHeight="1">
@@ -15028,13 +15023,13 @@
         <v>311</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>317</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="27.95" customHeight="1">
@@ -15042,13 +15037,13 @@
         <v>332</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>335</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="27.95" customHeight="1">
@@ -15056,13 +15051,13 @@
         <v>332</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>336</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="27.95" customHeight="1">
@@ -15070,13 +15065,13 @@
         <v>332</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>337</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="27.95" customHeight="1">
@@ -15084,13 +15079,13 @@
         <v>332</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>175</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="27.95" customHeight="1">
@@ -15098,13 +15093,13 @@
         <v>332</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>339</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="27.95" customHeight="1">
@@ -15112,13 +15107,13 @@
         <v>345</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="27.95" customHeight="1">
@@ -15126,13 +15121,13 @@
         <v>345</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C63" s="15" t="s">
         <v>349</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="27.95" customHeight="1">
@@ -15140,13 +15135,13 @@
         <v>345</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C64" s="15" t="s">
         <v>350</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="27.95" customHeight="1">
@@ -15154,13 +15149,13 @@
         <v>345</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>175</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="27.95" customHeight="1">
@@ -15168,13 +15163,13 @@
         <v>345</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C66" s="15" t="s">
         <v>208</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="27.95" customHeight="1">
@@ -15182,13 +15177,13 @@
         <v>357</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>286</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="27.95" customHeight="1">
@@ -15196,13 +15191,13 @@
         <v>357</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>360</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="27.95" customHeight="1">
@@ -15210,13 +15205,13 @@
         <v>357</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>361</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="27.95" customHeight="1">
@@ -15224,13 +15219,13 @@
         <v>357</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>274</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="27.95" customHeight="1">
@@ -15238,13 +15233,13 @@
         <v>357</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>363</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="27.95" customHeight="1">
@@ -15252,10 +15247,10 @@
         <v>369</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D72" s="16" t="s">
         <v>384</v>
@@ -15272,7 +15267,7 @@
         <v>372</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="27.95" customHeight="1">
@@ -15280,10 +15275,10 @@
         <v>388</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D74" s="16" t="s">
         <v>399</v>
@@ -15297,10 +15292,10 @@
         <v>97</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="27.95" customHeight="1">
@@ -15308,7 +15303,7 @@
         <v>402</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C76" s="15" t="s">
         <v>406</v>
@@ -15328,7 +15323,7 @@
         <v>407</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="27.95" customHeight="1">
@@ -15336,7 +15331,7 @@
         <v>415</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C78" s="15" t="s">
         <v>419</v>
@@ -15356,7 +15351,7 @@
         <v>420</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="27.95" customHeight="1">
@@ -15364,7 +15359,7 @@
         <v>430</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C80" s="15" t="s">
         <v>436</v>
@@ -15384,483 +15379,483 @@
         <v>437</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="27.95" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="27.95" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B83" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="27.95" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="27.95" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B85" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="27.95" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="27.95" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B87" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="27.95" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="27.95" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B89" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="27.95" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D90" s="16" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="27.95" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B91" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="27.95" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D92" s="16" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="27.95" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B93" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="27.95" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="D94" s="16" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="27.95" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B95" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="27.95" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="D96" s="16" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="27.95" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B97" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D97" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="27.95" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="D98" s="16" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="27.95" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B99" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D99" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="27.95" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="D100" s="16" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="27.95" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="B101" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="D101" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="27.95" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D102" s="16" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="27.95" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B103" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D103" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="27.95" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D104" s="16" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="27.95" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B105" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D105" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="27.95" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D106" s="16" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="27.95" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B107" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D107" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="27.95" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="27.95" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B109" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D109" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="27.95" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="27.95" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B111" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D111" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="27.95" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="27.95" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B113" s="15" t="s">
         <v>97</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="27.95" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="27.95" customHeight="1">
       <c r="A115" s="17" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B115" s="18" t="s">
         <v>97</v>
       </c>
       <c r="C115" s="18" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
   </sheetData>
@@ -15884,7 +15879,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="48" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -15898,86 +15893,86 @@
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="20" t="s">
+        <v>855</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>856</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>857</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>858</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>859</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>860</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="44.1" customHeight="1">
       <c r="A5" s="23" t="s">
+        <v>859</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>860</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>861</v>
+      </c>
+      <c r="D5" s="25" t="s">
         <v>862</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>863</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>864</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="44.1" customHeight="1">
       <c r="A6" s="23" t="s">
+        <v>863</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>864</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>865</v>
+      </c>
+      <c r="D6" s="25" t="s">
         <v>866</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>867</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>868</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="44.1" customHeight="1">
       <c r="A7" s="23" t="s">
+        <v>867</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>869</v>
+      </c>
+      <c r="D7" s="25" t="s">
         <v>870</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>871</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>872</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="44.1" customHeight="1">
       <c r="A8" s="23" t="s">
+        <v>871</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>872</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>873</v>
+      </c>
+      <c r="D8" s="25" t="s">
         <v>874</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>875</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>876</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="44.1" customHeight="1">
       <c r="A9" s="23" t="s">
+        <v>875</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>876</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>877</v>
+      </c>
+      <c r="D9" s="25" t="s">
         <v>878</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>879</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>880</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="44.1" customHeight="1">
@@ -15985,27 +15980,27 @@
         <v>134</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="44.1" customHeight="1">
       <c r="A11" s="23" t="s">
+        <v>882</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>883</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>884</v>
+      </c>
+      <c r="D11" s="25" t="s">
         <v>885</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>886</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>887</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="44.1" customHeight="1">
@@ -16013,13 +16008,13 @@
         <v>67</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="44.1" customHeight="1">
@@ -16027,13 +16022,13 @@
         <v>266</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="44.1" customHeight="1">
@@ -16041,27 +16036,27 @@
         <v>252</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="44.1" customHeight="1">
       <c r="A15" s="26" t="s">
+        <v>895</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>896</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>897</v>
+      </c>
+      <c r="D15" s="28" t="s">
         <v>898</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>899</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>900</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>901</v>
       </c>
     </row>
   </sheetData>
